--- a/Trắc nghiệm bài kiểm tra đánh giá đầu vào/da-metrics-easy.xlsx
+++ b/Trắc nghiệm bài kiểm tra đánh giá đầu vào/da-metrics-easy.xlsx
@@ -460,19 +460,19 @@
         <v>CAC (Customer Acquisition Cost) được tính bằng tổng chi phí sales &amp; marketing chia cho số lượng khách hàng mới thu hút được trong một khoảng thời gian.</v>
       </c>
       <c r="F2" t="str">
+        <v>Tỷ lệ phần trăm khách hàng hủy bỏ dịch vụ và không tiếp tục gia hạn hợp đồng — tỷ lệ khách hàng rời bỏ</v>
+      </c>
+      <c r="G2" t="str">
         <v>Tổng chi phí trung bình để thu hút được một khách hàng mới sử dụng sản phẩm hoặc dịch vụ — chi phí thu hút khách hàng</v>
       </c>
-      <c r="G2" t="str">
+      <c r="H2" t="str">
+        <v>Tổng chi phí tiền lương phải chi trả cho đội ngũ lập trình viên trong một tháng — chi phí phát triển</v>
+      </c>
+      <c r="I2" t="str">
         <v>Tổng doanh thu trung bình thu được từ một khách hàng trong suốt vòng đời của họ — doanh thu vòng đời khách hàng</v>
       </c>
-      <c r="H2" t="str">
-        <v>Tỷ lệ phần trăm khách hàng hủy bỏ dịch vụ và không tiếp tục gia hạn hợp đồng — tỷ lệ khách hàng rời bỏ</v>
-      </c>
-      <c r="I2" t="str">
-        <v>Tổng chi phí tiền lương phải chi trả cho đội ngũ lập trình viên trong một tháng — chi phí phát triển</v>
-      </c>
       <c r="J2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -492,19 +492,19 @@
         <v>LTV (Lifetime Value) đo lường tổng giá trị kinh tế mà một khách hàng đóng góp cho doanh nghiệp trong suốt toàn bộ mối quan hệ của họ với sản phẩm/dịch vụ.</v>
       </c>
       <c r="F3" t="str">
+        <v>Số tiền tối đa mà khách hàng sẵn sàng trả tiền để mua sản phẩm trong một giao dịch đơn lẻ — giá trị giao dịch tối đa</v>
+      </c>
+      <c r="G3" t="str">
         <v>Tổng doanh thu hoặc lợi nhuận ròng dự kiến mà một khách hàng mang lại cho doanh nghiệp trong suốt thời gian họ gắn bó — giá trị vòng đời khách hàng</v>
       </c>
-      <c r="G3" t="str">
-        <v>Số tiền tối đa mà khách hàng sẵn sàng trả tiền để mua sản phẩm trong một giao dịch đơn lẻ — giá trị giao dịch tối đa</v>
-      </c>
       <c r="H3" t="str">
+        <v>Tỷ lệ phần trăm khách hàng đánh giá 5 sao cho ứng dụng trên kho ứng dụng di động — tỷ lệ đánh giá tốt</v>
+      </c>
+      <c r="I3" t="str">
         <v>Số năm trung bình mà một nhân viên sales làm việc gắn bó tại công ty — thời gian gắn bó của nhân sự</v>
       </c>
-      <c r="I3" t="str">
-        <v>Tỷ lệ phần trăm khách hàng đánh giá 5 sao cho ứng dụng trên kho ứng dụng di động — tỷ lệ đánh giá tốt</v>
-      </c>
       <c r="J3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -527,10 +527,10 @@
         <v>Số lượng khách hàng ngưng sử dụng dịch vụ trong kỳ chia cho tổng số khách hàng đầu kỳ — tỷ lệ khách hàng rời bỏ</v>
       </c>
       <c r="G4" t="str">
+        <v>Số lượng đơn hàng bị lỗi kỹ thuật chia cho tổng số đơn hàng đã giao thành công — tỷ lệ lỗi đơn hàng</v>
+      </c>
+      <c r="H4" t="str">
         <v>Số lượng khách hàng đăng ký mới trong kỳ chia cho tổng số khách hàng cũ — tỷ lệ tăng trưởng khách</v>
-      </c>
-      <c r="H4" t="str">
-        <v>Số lượng đơn hàng bị lỗi kỹ thuật chia cho tổng số đơn hàng đã giao thành công — tỷ lệ lỗi đơn hàng</v>
       </c>
       <c r="I4" t="str">
         <v>Số tiền hoàn trả cho khách hàng chia cho tổng doanh thu bán hàng của doanh nghiệp — tỷ lệ hoàn tiền</v>
@@ -556,19 +556,19 @@
         <v>Phễu AARRR (Pirate Metrics) do Dave McClure đề xuất, là khung đo lường tiêu chuẩn cho các startup công nghệ để theo dõi toàn bộ vòng đời tương tác của khách hàng.</v>
       </c>
       <c r="F5" t="str">
+        <v>Analysis, Architecture, Requirements, Release, Retrospective — quy trình phát triển phần mềm</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Access, Authentication, Authorization, Audit, Administration — quy trình bảo mật thông tin</v>
+      </c>
+      <c r="H5" t="str">
         <v>Acquisition (Thu hút), Activation (Kích hoạt), Retention (Giữ chân), Referral (Giới thiệu), Revenue (Doanh thu) — phễu tăng trưởng AARRR</v>
       </c>
-      <c r="G5" t="str">
+      <c r="I5" t="str">
         <v>Advertising, Action, Research, Reporting, Review — quy trình tiếp thị trực tuyến</v>
       </c>
-      <c r="H5" t="str">
-        <v>Analysis, Architecture, Requirements, Release, Retrospective — quy trình phát triển phần mềm</v>
-      </c>
-      <c r="I5" t="str">
-        <v>Access, Authentication, Authorization, Audit, Administration — quy trình bảo mật thông tin</v>
-      </c>
       <c r="J5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -588,19 +588,19 @@
         <v>AOV (Average Order Value) đo lường số tiền trung bình khách hàng chi tiêu cho mỗi lần mua hàng. Tăng AOV (qua up-sell, cross-sell) là cách nhanh để tăng doanh thu mà không cần tăng chi phí CAC.</v>
       </c>
       <c r="F6" t="str">
+        <v>Tổng số lượng sản phẩm bán ra chia cho tổng số lượng đơn hàng — số sản phẩm trung bình mỗi đơn</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Tổng số lượng khách hàng truy cập website chia cho tổng số đơn hàng được tạo — tỷ lệ chuyển đổi đơn</v>
+      </c>
+      <c r="H6" t="str">
         <v>Tổng doanh thu chia cho tổng số lượng đơn hàng trong một khoảng thời gian — giá trị đơn hàng trung bình</v>
       </c>
-      <c r="G6" t="str">
-        <v>Tổng số lượng sản phẩm bán ra chia cho tổng số lượng đơn hàng — số sản phẩm trung bình mỗi đơn</v>
-      </c>
-      <c r="H6" t="str">
+      <c r="I6" t="str">
         <v>Tổng chi phí quảng cáo trực tuyến chia cho tổng số đơn hàng thành công — chi phí quảng cáo mỗi đơn</v>
       </c>
-      <c r="I6" t="str">
-        <v>Tổng số lượng khách hàng truy cập website chia cho tổng số đơn hàng được tạo — tỷ lệ chuyển đổi đơn</v>
-      </c>
       <c r="J6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -620,19 +620,19 @@
         <v>MRR (Monthly Recurring Revenue) đo lường lượng doanh thu có tính chất lặp lại, dự đoán trước được mà doanh nghiệp SaaS nhận được hàng tháng từ các gói thuê bao hoạt động.</v>
       </c>
       <c r="F7" t="str">
+        <v>Mô hình nhận thầu xây dựng các công trình hạ tầng kỹ thuật quốc gia — nhận thầu xây dựng</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Mô hình đấu giá tài sản trực tuyến qua mạng internet — đấu giá tài sản</v>
+      </c>
+      <c r="H7" t="str">
         <v>Mô hình phần mềm dạng dịch vụ trả phí đăng ký định kỳ (SaaS / Subscription) — doanh thu định kỳ hàng tháng</v>
       </c>
-      <c r="G7" t="str">
+      <c r="I7" t="str">
         <v>Mô hình bán lẻ truyền thống thanh toán trực tiếp một lần tại quầy — bán lẻ một lần</v>
       </c>
-      <c r="H7" t="str">
-        <v>Mô hình đấu giá tài sản trực tuyến qua mạng internet — đấu giá tài sản</v>
-      </c>
-      <c r="I7" t="str">
-        <v>Mô hình nhận thầu xây dựng các công trình hạ tầng kỹ thuật quốc gia — nhận thầu xây dựng</v>
-      </c>
       <c r="J7">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -655,13 +655,13 @@
         <v>Phân tích và theo dõi hành vi của một nhóm người dùng có chung một đặc điểm xuất phát điểm trong một khoảng thời gian (ví dụ: nhóm khách hàng đăng ký vào tháng 1) — phân tích nhóm khách hàng đồng thời kỳ</v>
       </c>
       <c r="G8" t="str">
-        <v>Phân tích cấu trúc bảng dữ liệu của hệ quản trị cơ sở dữ liệu quan hệ — phân tích database</v>
+        <v>Biểu đồ so sánh mức độ hài lòng của khách hàng đối với 5 đối thủ cạnh tranh lớn nhất — so sánh đối thủ</v>
       </c>
       <c r="H8" t="str">
         <v>Đo lường thời gian trễ trung bình của các API kết nối với cổng thanh toán — phân tích hiệu năng hệ thống</v>
       </c>
       <c r="I8" t="str">
-        <v>Biểu đồ so sánh mức độ hài lòng của khách hàng đối với 5 đối thủ cạnh tranh lớn nhất — so sánh đối thủ</v>
+        <v>Phân tích cấu trúc bảng dữ liệu của hệ quản trị cơ sở dữ liệu quan hệ — phân tích database</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -684,19 +684,19 @@
         <v>NPS được tính dựa trên câu hỏi: "Trên thang điểm từ 0-10, khả năng bạn giới thiệu sản phẩm này cho bạn bè là bao nhiêu?". Khách hàng chọn 9-10 là Promoters (Người ủng hộ), 7-8 là Passives, 0-6 là Detractors (Người gièm pha). NPS = %Promoters - %Detractors.</v>
       </c>
       <c r="F9" t="str">
+        <v>Tổng số tiền tối đa khách hàng đã chi tiêu trên ứng dụng di động trong một năm — tổng chi tiêu khách hàng</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Tỷ lệ phần trăm khách hàng tự thực hiện đăng ký tài khoản thành công mà không cần hỗ trợ — tỷ lệ tự đăng ký</v>
+      </c>
+      <c r="H9" t="str">
         <v>Mức độ hài lòng và lòng trung thành của khách hàng thông qua khả năng họ sẵn sàng giới thiệu sản phẩm cho người khác — chỉ số đo lường lòng trung thành</v>
       </c>
-      <c r="G9" t="str">
-        <v>Tổng số tiền tối đa khách hàng đã chi tiêu trên ứng dụng di động trong một năm — tổng chi tiêu khách hàng</v>
-      </c>
-      <c r="H9" t="str">
+      <c r="I9" t="str">
         <v>Tốc độ tải trang trung bình của ứng dụng di động trên thiết bị của khách hàng — tốc độ ứng dụng khách</v>
       </c>
-      <c r="I9" t="str">
-        <v>Tỷ lệ phần trăm khách hàng tự thực hiện đăng ký tài khoản thành công mà không cần hỗ trợ — tỷ lệ tự đăng ký</v>
-      </c>
       <c r="J9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -719,13 +719,13 @@
         <v>Tổng số lượng giao dịch thành công chia cho tổng số lượng khách truy cập (sessions/visitors) vào website — tỷ lệ chuyển đổi mua hàng</v>
       </c>
       <c r="G10" t="str">
-        <v>Tổng số lượng sản phẩm thêm vào giỏ hàng chia cho tổng số lượng sản phẩm có trong kho — tỷ lệ giỏ hàng</v>
+        <v>Tổng số lượng bài viết đăng tải trên trang tin tức chia cho tổng số lượt like của người dùng — tỷ lệ tương tác bài viết</v>
       </c>
       <c r="H10" t="str">
         <v>Tổng số tiền chi tiêu quảng cáo chia cho tổng doanh thu thu được từ đơn hàng — tỷ lệ chi phí doanh thu</v>
       </c>
       <c r="I10" t="str">
-        <v>Tổng số lượng bài viết đăng tải trên trang tin tức chia cho tổng số lượt like của người dùng — tỷ lệ tương tác bài viết</v>
+        <v>Tổng số lượng sản phẩm thêm vào giỏ hàng chia cho tổng số lượng sản phẩm có trong kho — tỷ lệ giỏ hàng</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -748,19 +748,19 @@
         <v>ROI = (Lợi nhuận ròng - Chi phí đầu tư) / Chi phí đầu tư. Chỉ số này thể hiện hiệu quả sử dụng vốn của một hoạt động đầu tư (ví dụ chạy chiến dịch quảng cáo).</v>
       </c>
       <c r="F11" t="str">
+        <v>Tổng thời gian cần thiết để đội ngũ lập trình viên hoàn thành việc viết code — tiến độ hoàn thành</v>
+      </c>
+      <c r="G11" t="str">
+        <v>Số lượng lỗi bảo mật tối đa được phát hiện và vá thành công trong hệ thống — chỉ số an ninh</v>
+      </c>
+      <c r="H11" t="str">
         <v>Tỷ lệ lợi nhuận ròng thu về so với tổng chi phí đầu tư ban đầu của một chiến dịch hoặc dự án — tỷ suất hoàn vốn đầu tư</v>
-      </c>
-      <c r="G11" t="str">
-        <v>Tổng thời gian cần thiết để đội ngũ lập trình viên hoàn thành việc viết code — tiến độ hoàn thành</v>
-      </c>
-      <c r="H11" t="str">
-        <v>Số lượng lỗi bảo mật tối đa được phát hiện và vá thành công trong hệ thống — chỉ số an ninh</v>
       </c>
       <c r="I11" t="str">
         <v>Tỷ lệ phần trăm khách hàng đồng ý nhận email quảng cáo hàng tuần của công ty — tỷ lệ nhận email quảng cáo</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
